--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/08,09,26 ПОКОМ КИ/дв 08,09,26 бррсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/09,26/08,09,26 ПОКОМ КИ/дв 08,09,26 бррсч пок ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\09,26\08,09,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44265A38-494A-4C9A-AAE4-89BBAA2175FC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A960D41-D467-49A3-B516-C80BEEF312AE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="765" uniqueCount="391">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -1258,7 +1258,10 @@
     <t>на списание</t>
   </si>
   <si>
-    <t>итого</t>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>13,09,</t>
   </si>
 </sst>
 </file>
@@ -2020,7 +2023,9 @@
         <v>24</v>
       </c>
       <c r="T4" s="12"/>
-      <c r="U4" s="12"/>
+      <c r="U4" s="12" t="s">
+        <v>390</v>
+      </c>
       <c r="V4" s="12"/>
       <c r="W4" s="12"/>
       <c r="X4" s="12" t="s">
@@ -2506,7 +2511,7 @@
       </c>
       <c r="T9" s="11"/>
       <c r="U9" s="4">
-        <f t="shared" ref="U7:U70" si="8">T9</f>
+        <f t="shared" ref="U9:U70" si="8">T9</f>
         <v>0</v>
       </c>
       <c r="V9" s="12" t="e">
